--- a/data/trans_dic/IP1006-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1006-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen cardiopatía congénita</t>
+          <t>Menores que padecen cardiopatía congénita (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,37 +678,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -717,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
     </row>
@@ -1012,37 +1013,37 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,99</t>
+          <t>0,3; 3,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,72</t>
+          <t>0,3; 1,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1117,32 +1118,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,3</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,07</t>
+          <t>0,4; 4,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,14</t>
+          <t>0,48; 5,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1152,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,52</t>
+          <t>0,24; 2,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,33</t>
+          <t>0,23; 2,32</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,49</t>
+          <t>0,0; 7,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,8</t>
+          <t>0,08; 0,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,02</t>
+          <t>0,13; 1,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,86</t>
+          <t>0,1; 0,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,54</t>
+          <t>0,4; 1,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,85</t>
+          <t>0,09; 0,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,61</t>
+          <t>0,13; 0,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,9</t>
+          <t>0,25; 0,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,69</t>
+          <t>0,14; 0,68</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen cardiopatía congénita (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3330</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3344</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3881</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3506</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3204</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2816</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2772</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3495</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3350</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3034</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2792</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>674; 6873</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4939</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1311; 7553</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3048</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2073</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2522</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2522</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2699</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>540; 6553</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3609</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>677; 7140</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3118</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4913</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>680; 7487</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>653; 6486</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2420</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5271</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2621</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4005</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1849</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2673</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3949</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>7234</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4672</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>521; 5259</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4768</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>878; 7270</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>685; 5606</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2840; 11498</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>620; 5461</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1686; 8793</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>3453; 13357</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1934; 9333</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1006-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1006-Clase-trans_dic.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
     </row>
@@ -1008,27 +1008,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,62</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,63</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,36</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,03</t>
+          <t>0,29; 2,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,75</t>
+          <t>0,29; 1,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,37 +1128,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,81</t>
+          <t>0,39; 4,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,11</t>
+          <t>0,49; 5,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,59</t>
+          <t>0,23; 2,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,32</t>
+          <t>0,24; 2,31</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,77</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,82</t>
+          <t>0,08; 0,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,08</t>
+          <t>0,1; 1,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,82</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,61</t>
+          <t>0,38; 1,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,77</t>
+          <t>0,09; 0,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,66</t>
+          <t>0,1; 0,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,96</t>
+          <t>0,27; 0,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,68</t>
+          <t>0,14; 0,66</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3330</t>
+          <t>0; 3617</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3344</t>
+          <t>0; 3398</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3881</t>
+          <t>0; 3012</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3506</t>
+          <t>0; 3467</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3204</t>
+          <t>0; 3281</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2816</t>
+          <t>0; 4178</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2772</t>
+          <t>0; 3560</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3495</t>
+          <t>0; 3586</t>
         </is>
       </c>
     </row>
@@ -2128,27 +2128,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3235</t>
+          <t>0; 3218</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3350</t>
+          <t>0; 3321</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3034</t>
+          <t>0; 3642</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2792</t>
+          <t>0; 4112</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>674; 6873</t>
+          <t>661; 6362</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2158,17 +2158,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4939</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1311; 7553</t>
+          <t>1243; 7509</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3048</t>
+          <t>0; 3474</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3188</t>
+          <t>0; 3045</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2301,37 +2301,37 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>540; 6553</t>
+          <t>537; 5454</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3609</t>
+          <t>0; 3624</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>677; 7140</t>
+          <t>684; 7121</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3118</t>
+          <t>0; 3602</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4913</t>
+          <t>0; 5014</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>680; 7487</t>
+          <t>677; 7647</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>653; 6486</t>
+          <t>657; 6443</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2420</t>
+          <t>0; 2674</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5271</t>
+          <t>0; 3432</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2621</t>
+          <t>0; 2928</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4005</t>
+          <t>0; 4074</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>521; 5259</t>
+          <t>521; 5287</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4768</t>
+          <t>0; 4746</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>878; 7270</t>
+          <t>656; 6704</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>685; 5606</t>
+          <t>0; 6286</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2840; 11498</t>
+          <t>2697; 10973</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>620; 5461</t>
+          <t>626; 6002</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1686; 8793</t>
+          <t>1371; 8084</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3453; 13357</t>
+          <t>3682; 12878</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1934; 9333</t>
+          <t>1960; 9184</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1006-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1006-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,22 +630,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,71</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,29; 2,99</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,61</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,62</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,63</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,03</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,29; 2,8</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,74</t>
+          <t>0,29; 1,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,49; 5,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,0</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 3,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,39; 4,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,65</t>
+          <t>0,23; 2,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,31</t>
+          <t>0,23; 2,33</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,83</t>
+          <t>0,1; 0,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>0,36; 1,54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0,09; 0,85</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,8</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,7</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 1,0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,92</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 1,54</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,85</t>
+          <t>0,1; 1,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,61</t>
+          <t>0,11; 0,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,93</t>
+          <t>0,25; 0,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,66</t>
+          <t>0,14; 0,69</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3380</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3617</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3398</t>
+          <t>0; 3347</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>685</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3473</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4250</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3467</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3432</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3281</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4178</t>
+          <t>0; 3453</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3560</t>
+          <t>0; 3080</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3586</t>
+          <t>0; 3208</t>
         </is>
       </c>
     </row>
@@ -2027,27 +2027,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>600</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2700</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>0; 3450</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3321</t>
+          <t>668; 6785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3642</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4112</t>
+          <t>0; 3228</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>661; 6362</t>
+          <t>0; 3281</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2671</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>0; 4637</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1243; 7509</t>
+          <t>1247; 7451</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3474</t>
+          <t>0; 3054</t>
         </is>
       </c>
     </row>
@@ -2190,27 +2190,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2522</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>683</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2073</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2522</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3045</t>
+          <t>0; 3966</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>679; 7193</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>537; 5454</t>
+          <t>0; 4100</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3624</t>
+          <t>0; 3435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>684; 7121</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3602</t>
+          <t>536; 5539</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5014</t>
+          <t>0; 4906</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>677; 7647</t>
+          <t>678; 7279</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>657; 6443</t>
+          <t>648; 6519</t>
         </is>
       </c>
     </row>
@@ -2348,22 +2348,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,24 +2401,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2674</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3723</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3174</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3432</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2928</t>
+          <t>0; 3048</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4074</t>
+          <t>0; 4157</t>
         </is>
       </c>
     </row>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>1849</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1346</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2673</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>521; 5287</t>
+          <t>683; 5919</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4746</t>
+          <t>2577; 10986</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>656; 6704</t>
+          <t>625; 6030</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 6286</t>
+          <t>523; 5119</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2697; 10973</t>
+          <t>0; 4690</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>626; 6002</t>
+          <t>665; 6837</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1371; 8084</t>
+          <t>1410; 8016</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3682; 12878</t>
+          <t>3420; 12476</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1960; 9184</t>
+          <t>1939; 9477</t>
         </is>
       </c>
     </row>
